--- a/stat_arb/fi static data.xlsx
+++ b/stat_arb/fi static data.xlsx
@@ -8,26 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micha\git-crypto\crypto-project\stat_arb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB43D364-5E37-4AF8-A117-CB9D3D48602E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AB7A8C5-B833-437C-AE7E-26F6EDD4AAA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="2" xr2:uid="{15B058D3-9D37-4F2B-827B-BDA2ACAE02FA}"/>
+    <workbookView xWindow="30645" yWindow="3210" windowWidth="24060" windowHeight="13095" firstSheet="3" activeTab="11" xr2:uid="{15B058D3-9D37-4F2B-827B-BDA2ACAE02FA}"/>
   </bookViews>
   <sheets>
-    <sheet name="AGG" sheetId="2" r:id="rId1"/>
-    <sheet name="CA MUNIS" sheetId="3" r:id="rId2"/>
-    <sheet name="CONVERTS" sheetId="5" r:id="rId3"/>
-    <sheet name="CORPS" sheetId="6" r:id="rId4"/>
-    <sheet name="EM MKTS" sheetId="7" r:id="rId5"/>
-    <sheet name="FALN ANGLS" sheetId="8" r:id="rId6"/>
-    <sheet name="HI YLD" sheetId="1" r:id="rId7"/>
-    <sheet name="INTL AGG" sheetId="9" r:id="rId8"/>
-    <sheet name="INTL TSY" sheetId="10" r:id="rId9"/>
-    <sheet name="LT CORPS" sheetId="11" r:id="rId10"/>
-    <sheet name="LT TSY" sheetId="12" r:id="rId11"/>
-    <sheet name="MORTGAGES" sheetId="13" r:id="rId12"/>
-    <sheet name="MUNIS" sheetId="4" r:id="rId13"/>
-    <sheet name="PREFS" sheetId="14" r:id="rId14"/>
-    <sheet name="REAL ESTATE" sheetId="15" r:id="rId15"/>
+    <sheet name="Sheet1" sheetId="16" r:id="rId1"/>
+    <sheet name="AGG" sheetId="2" r:id="rId2"/>
+    <sheet name="CA MUNIS" sheetId="3" r:id="rId3"/>
+    <sheet name="CONVERTS" sheetId="5" r:id="rId4"/>
+    <sheet name="CORPS" sheetId="6" r:id="rId5"/>
+    <sheet name="EM MKTS" sheetId="7" r:id="rId6"/>
+    <sheet name="FALN ANGLS" sheetId="8" r:id="rId7"/>
+    <sheet name="HI YLD" sheetId="1" r:id="rId8"/>
+    <sheet name="INTL AGG" sheetId="9" r:id="rId9"/>
+    <sheet name="INTL TSY" sheetId="10" r:id="rId10"/>
+    <sheet name="LT CORPS" sheetId="11" r:id="rId11"/>
+    <sheet name="LT TSY" sheetId="12" r:id="rId12"/>
+    <sheet name="MORTGAGES" sheetId="13" r:id="rId13"/>
+    <sheet name="MUNIS" sheetId="4" r:id="rId14"/>
+    <sheet name="PREFS" sheetId="14" r:id="rId15"/>
+    <sheet name="REAL ESTATE" sheetId="15" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="274">
   <si>
     <t>SPHY</t>
   </si>
@@ -824,6 +825,57 @@
   </si>
   <si>
     <t>2026 has weird results</t>
+  </si>
+  <si>
+    <t>days</t>
+  </si>
+  <si>
+    <t>Leverage</t>
+  </si>
+  <si>
+    <t>agg_no_IUSB</t>
+  </si>
+  <si>
+    <t>ca_munis</t>
+  </si>
+  <si>
+    <t>converts</t>
+  </si>
+  <si>
+    <t>corps</t>
+  </si>
+  <si>
+    <t>em_mkts</t>
+  </si>
+  <si>
+    <t>faln_agls</t>
+  </si>
+  <si>
+    <t>hi_yld</t>
+  </si>
+  <si>
+    <t>intl_agg</t>
+  </si>
+  <si>
+    <t>intl_tsy</t>
+  </si>
+  <si>
+    <t>lt_corps</t>
+  </si>
+  <si>
+    <t>lt_tsy_no_TLT</t>
+  </si>
+  <si>
+    <t>mortgages</t>
+  </si>
+  <si>
+    <t>munis</t>
+  </si>
+  <si>
+    <t>prefs</t>
+  </si>
+  <si>
+    <t>real_estate</t>
   </si>
 </sst>
 </file>
@@ -962,7 +1014,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1024,6 +1076,7 @@
     </xf>
     <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1401,16 +1454,1285 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C5D3543-9F79-4445-B7E7-46619BBF5A6C}">
+  <dimension ref="A5:K14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>259</v>
+      </c>
+      <c r="D5" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>262</v>
+      </c>
+      <c r="D6" t="s">
+        <v>261</v>
+      </c>
+      <c r="K6" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>265</v>
+      </c>
+      <c r="D7" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>268</v>
+      </c>
+      <c r="D8" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
+        <v>270</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29CCCBDC-E4C7-4EFC-80EF-4EF2998B8A6B}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28.7109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="25" style="14" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B1" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="6">
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="C3" s="6">
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+    </row>
+    <row r="4" spans="1:7" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" s="18">
+        <v>5.1310000000000001E-2</v>
+      </c>
+      <c r="C9" s="18">
+        <v>0.58701999999999999</v>
+      </c>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{766D49F6-C037-4EC1-BF65-3DBCF70ACA86}">
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B1" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="C3" s="15">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="D3" s="15">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="E3" s="5"/>
+    </row>
+    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="E4" s="11"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D6" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D7" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" s="8">
+        <v>9.6627000000000005E-2</v>
+      </c>
+      <c r="C9" s="8">
+        <v>0.21740999999999999</v>
+      </c>
+      <c r="D9" s="8">
+        <v>0.34920000000000001</v>
+      </c>
+      <c r="E9" s="8"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E10" s="8"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="8"/>
+    </row>
+    <row r="12" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="B12" s="15">
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="C12" s="15">
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="D12" s="15">
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="E12" s="8"/>
+      <c r="F12"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E13" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2BD3974-BBBF-4151-9DCA-06B6B270A79F}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="25" customWidth="1"/>
+    <col min="5" max="5" width="25" style="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B1" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="E1" s="29" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="30" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="C3" s="15">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="D3" s="15">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="E3" s="31">
+        <v>1.5E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C6" t="s">
+        <v>191</v>
+      </c>
+      <c r="D6" t="s">
+        <v>192</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C7" t="s">
+        <v>194</v>
+      </c>
+      <c r="D7" t="s">
+        <v>195</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" s="8">
+        <v>9.2302999999999996E-2</v>
+      </c>
+      <c r="C9" s="8">
+        <v>0.127</v>
+      </c>
+      <c r="D9" s="8">
+        <v>0.214</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="30" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B12" s="5">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="C12" s="35">
+        <v>0.11</v>
+      </c>
+      <c r="D12" s="5">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="E12" s="31">
+        <v>6.6000000000000003E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC0E5440-676C-4B03-880D-1E971EA1A06F}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="25" customWidth="1"/>
+    <col min="5" max="5" width="25" style="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B1" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="E1" s="29"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="C3" s="15">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="D3" s="15">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="E3" s="31"/>
+    </row>
+    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="E4" s="32"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>206</v>
+      </c>
+      <c r="C6" t="s">
+        <v>207</v>
+      </c>
+      <c r="D6" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" t="s">
+        <v>209</v>
+      </c>
+      <c r="C7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" s="8">
+        <v>0.14300099999999999</v>
+      </c>
+      <c r="C9" s="8">
+        <v>0.15989999999999999</v>
+      </c>
+      <c r="D9" s="8">
+        <v>0.33404800000000001</v>
+      </c>
+      <c r="E9" s="33"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="E10" s="27"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61E69EB6-34F9-489A-A4BE-0E0038F4A3DA}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="25" customWidth="1"/>
+    <col min="5" max="5" width="25" style="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B1" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="29"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5">
+        <v>2.3E-3</v>
+      </c>
+      <c r="C3" s="15">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="D3" s="15">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E3" s="31"/>
+    </row>
+    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="E4" s="32"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C6" t="s">
+        <v>222</v>
+      </c>
+      <c r="D6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="C7" t="s">
+        <v>225</v>
+      </c>
+      <c r="D7" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" s="8">
+        <v>0.13450999999999999</v>
+      </c>
+      <c r="C9" s="8">
+        <v>0.14169999999999999</v>
+      </c>
+      <c r="D9" s="8">
+        <v>0.285497</v>
+      </c>
+      <c r="E9" s="33"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E10" s="27"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3A18E9A-5FEA-4795-8589-22D9122D0132}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="25" customWidth="1"/>
+    <col min="5" max="5" width="25" style="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B1" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D1" s="4"/>
+      <c r="E1" s="29"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="6">
+        <v>2.3E-3</v>
+      </c>
+      <c r="C3" s="6">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="D3" s="15"/>
+      <c r="E3" s="31"/>
+    </row>
+    <row r="4" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="D4" s="17"/>
+      <c r="E4" s="32"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>246</v>
+      </c>
+      <c r="C6" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" t="s">
+        <v>250</v>
+      </c>
+      <c r="C8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="C9" s="8">
+        <v>6.5883999999999998E-2</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="33"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="D10" s="20"/>
+      <c r="E10" s="27"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" t="s">
+        <v>252</v>
+      </c>
+      <c r="C11" t="s">
+        <v>252</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8716025D-6040-4D17-B4EA-B59A0DAE7C7F}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="25" customWidth="1"/>
+    <col min="5" max="5" width="25" style="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B1" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="D1" s="4"/>
+      <c r="E1" s="29"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="C3" s="15">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="D3" s="15"/>
+      <c r="E3" s="31"/>
+    </row>
+    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="D4" s="17"/>
+      <c r="E4" s="32"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>233</v>
+      </c>
+      <c r="C6" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>237</v>
+      </c>
+      <c r="C8" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="8">
+        <v>0.22220000000000001</v>
+      </c>
+      <c r="C9" s="8">
+        <v>0.695461</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="33"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="D10" s="20"/>
+      <c r="E10" s="27"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" t="s">
+        <v>240</v>
+      </c>
+      <c r="C11" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B12" s="5">
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0.16500000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{827A2E32-66D5-4C34-8BDA-1D2CD6AF4352}">
   <dimension ref="A1:K40"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.88671875" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.85546875" style="12" bestFit="1" customWidth="1"/>
     <col min="2" max="7" width="25" style="14" customWidth="1"/>
-    <col min="8" max="16384" width="9.109375" style="14"/>
+    <col min="8" max="16384" width="9.140625" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
         <v>46</v>
       </c>
@@ -1428,7 +2750,7 @@
       </c>
       <c r="G1" s="13"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>7</v>
       </c>
@@ -1448,7 +2770,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>6</v>
       </c>
@@ -1469,7 +2791,7 @@
       </c>
       <c r="G3" s="15"/>
     </row>
-    <row r="4" spans="1:11" s="17" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>10</v>
       </c>
@@ -1489,7 +2811,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>11</v>
       </c>
@@ -1509,7 +2831,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>8</v>
       </c>
@@ -1529,7 +2851,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>60</v>
       </c>
@@ -1549,7 +2871,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>35</v>
       </c>
@@ -1569,7 +2891,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>66</v>
       </c>
@@ -1590,7 +2912,7 @@
       </c>
       <c r="G9" s="18"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>67</v>
       </c>
@@ -1611,7 +2933,7 @@
       </c>
       <c r="G10" s="20"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>72</v>
       </c>
@@ -1631,16 +2953,43 @@
         <v>73</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="12" t="s">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="B12" s="15">
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="C12" s="15">
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="D12" s="15">
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="E12" s="15">
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="F12" s="15">
+        <v>0.16500000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="12">
+        <v>20</v>
+      </c>
+      <c r="B15" s="12" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
         <v>254</v>
       </c>
-      <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
@@ -1651,7 +3000,7 @@
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
       <c r="B17" s="34"/>
       <c r="C17" s="34"/>
@@ -1664,7 +3013,7 @@
       <c r="J17" s="34"/>
       <c r="K17" s="34"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="34"/>
       <c r="C18" s="34"/>
@@ -1677,7 +3026,7 @@
       <c r="J18" s="34"/>
       <c r="K18" s="34"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" s="34"/>
       <c r="C19" s="34"/>
@@ -1690,7 +3039,7 @@
       <c r="J19" s="34"/>
       <c r="K19" s="34"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
       <c r="B20" s="34"/>
       <c r="C20" s="34"/>
@@ -1703,7 +3052,7 @@
       <c r="J20" s="34"/>
       <c r="K20" s="34"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
       <c r="B21" s="34"/>
       <c r="C21" s="34"/>
@@ -1716,7 +3065,7 @@
       <c r="J21" s="34"/>
       <c r="K21" s="34"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="B22" s="34"/>
       <c r="C22" s="34"/>
@@ -1729,7 +3078,7 @@
       <c r="J22" s="34"/>
       <c r="K22" s="34"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="B23" s="34"/>
       <c r="C23" s="34"/>
@@ -1742,7 +3091,7 @@
       <c r="J23" s="34"/>
       <c r="K23" s="34"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="B24" s="34"/>
       <c r="C24" s="34"/>
@@ -1755,7 +3104,7 @@
       <c r="J24" s="34"/>
       <c r="K24" s="34"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
       <c r="B25" s="34"/>
       <c r="C25" s="34"/>
@@ -1768,7 +3117,7 @@
       <c r="J25" s="34"/>
       <c r="K25" s="34"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
       <c r="B26" s="34"/>
       <c r="C26" s="34"/>
@@ -1781,7 +3130,7 @@
       <c r="J26" s="34"/>
       <c r="K26" s="34"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -1794,7 +3143,7 @@
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
       <c r="B31" s="34"/>
       <c r="C31" s="34"/>
@@ -1807,7 +3156,7 @@
       <c r="J31" s="34"/>
       <c r="K31" s="34"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
       <c r="B32" s="34"/>
       <c r="C32" s="34"/>
@@ -1820,7 +3169,7 @@
       <c r="J32" s="34"/>
       <c r="K32" s="34"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
       <c r="B33" s="34"/>
       <c r="C33" s="34"/>
@@ -1833,7 +3182,7 @@
       <c r="J33" s="34"/>
       <c r="K33" s="34"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
       <c r="B34" s="34"/>
       <c r="C34" s="34"/>
@@ -1846,7 +3195,7 @@
       <c r="J34" s="34"/>
       <c r="K34" s="34"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
       <c r="B35" s="34"/>
       <c r="C35" s="34"/>
@@ -1859,7 +3208,7 @@
       <c r="J35" s="34"/>
       <c r="K35" s="34"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
       <c r="B36" s="34"/>
       <c r="C36" s="34"/>
@@ -1872,7 +3221,7 @@
       <c r="J36" s="34"/>
       <c r="K36" s="34"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
       <c r="B37" s="34"/>
       <c r="C37" s="34"/>
@@ -1885,7 +3234,7 @@
       <c r="J37" s="34"/>
       <c r="K37" s="34"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
       <c r="B38" s="34"/>
       <c r="C38" s="34"/>
@@ -1898,7 +3247,7 @@
       <c r="J38" s="34"/>
       <c r="K38" s="34"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
       <c r="B39" s="34"/>
       <c r="C39" s="34"/>
@@ -1911,7 +3260,7 @@
       <c r="J39" s="34"/>
       <c r="K39" s="34"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
       <c r="B40" s="34"/>
       <c r="C40" s="34"/>
@@ -1937,1014 +3286,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{766D49F6-C037-4EC1-BF65-3DBCF70ACA86}">
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E46188D4-5281-4A43-BB5D-4640E9D5F481}">
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="25" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="25" style="14" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="E1" s="4"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="5">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="C3" s="15">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="D3" s="15">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="E3" s="5"/>
-    </row>
-    <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="E4" s="11"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>174</v>
-      </c>
-      <c r="C6" t="s">
-        <v>175</v>
-      </c>
-      <c r="D6" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" t="s">
-        <v>177</v>
-      </c>
-      <c r="C7" t="s">
-        <v>178</v>
-      </c>
-      <c r="D7" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B8" t="s">
-        <v>98</v>
-      </c>
-      <c r="C8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D8" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B9" s="8">
-        <v>9.6627000000000005E-2</v>
-      </c>
-      <c r="C9" s="8">
-        <v>0.21740999999999999</v>
-      </c>
-      <c r="D9" s="8">
-        <v>0.34920000000000001</v>
-      </c>
-      <c r="E9" s="8"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E10" s="3"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" t="s">
-        <v>75</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2BD3974-BBBF-4151-9DCA-06B6B270A79F}">
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="25" customWidth="1"/>
-    <col min="5" max="5" width="25" style="30" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E1" s="29" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="30" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="5">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="C3" s="15">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="D3" s="15">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="E3" s="31">
-        <v>1.5E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="E4" s="32" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="30" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>190</v>
-      </c>
-      <c r="C6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D6" t="s">
-        <v>192</v>
-      </c>
-      <c r="E6" s="30" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" t="s">
-        <v>155</v>
-      </c>
-      <c r="C7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D7" t="s">
-        <v>195</v>
-      </c>
-      <c r="E7" s="30" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B8" t="s">
-        <v>98</v>
-      </c>
-      <c r="C8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D8" t="s">
-        <v>98</v>
-      </c>
-      <c r="E8" s="30" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B9" s="8">
-        <v>9.2302999999999996E-2</v>
-      </c>
-      <c r="C9" s="8">
-        <v>0.127</v>
-      </c>
-      <c r="D9" s="8">
-        <v>0.214</v>
-      </c>
-      <c r="E9" s="33" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E11" s="30" t="s">
-        <v>73</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC0E5440-676C-4B03-880D-1E971EA1A06F}">
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="25" customWidth="1"/>
-    <col min="5" max="5" width="25" style="30" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="E1" s="29"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="5">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="C3" s="15">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="D3" s="15">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="E3" s="31"/>
-    </row>
-    <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>204</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>205</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>204</v>
-      </c>
-      <c r="E4" s="32"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>206</v>
-      </c>
-      <c r="C6" t="s">
-        <v>207</v>
-      </c>
-      <c r="D6" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" t="s">
-        <v>209</v>
-      </c>
-      <c r="C7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B8" t="s">
-        <v>98</v>
-      </c>
-      <c r="C8" t="s">
-        <v>98</v>
-      </c>
-      <c r="D8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B9" s="8">
-        <v>0.14300099999999999</v>
-      </c>
-      <c r="C9" s="8">
-        <v>0.15989999999999999</v>
-      </c>
-      <c r="D9" s="8">
-        <v>0.33404800000000001</v>
-      </c>
-      <c r="E9" s="33"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>212</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="E10" s="27"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" t="s">
-        <v>75</v>
-      </c>
-      <c r="D11" t="s">
-        <v>73</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61E69EB6-34F9-489A-A4BE-0E0038F4A3DA}">
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="25" customWidth="1"/>
-    <col min="5" max="5" width="25" style="30" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="E1" s="29"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>217</v>
-      </c>
-      <c r="C2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="5">
-        <v>2.3E-3</v>
-      </c>
-      <c r="C3" s="15">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="D3" s="15">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="E3" s="31"/>
-    </row>
-    <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>218</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>219</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>220</v>
-      </c>
-      <c r="E4" s="32"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>221</v>
-      </c>
-      <c r="C6" t="s">
-        <v>222</v>
-      </c>
-      <c r="D6" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="C7" t="s">
-        <v>225</v>
-      </c>
-      <c r="D7" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B8" t="s">
-        <v>98</v>
-      </c>
-      <c r="C8" t="s">
-        <v>98</v>
-      </c>
-      <c r="D8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B9" s="8">
-        <v>0.13450999999999999</v>
-      </c>
-      <c r="C9" s="8">
-        <v>0.14169999999999999</v>
-      </c>
-      <c r="D9" s="8">
-        <v>0.285497</v>
-      </c>
-      <c r="E9" s="33"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="E10" s="27"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" t="s">
-        <v>75</v>
-      </c>
-      <c r="D11" t="s">
-        <v>73</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3A18E9A-5FEA-4795-8589-22D9122D0132}">
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="25" customWidth="1"/>
-    <col min="5" max="5" width="25" style="30" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="29"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="6">
-        <v>2.3E-3</v>
-      </c>
-      <c r="C3" s="6">
-        <v>4.4999999999999997E-3</v>
-      </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="31"/>
-    </row>
-    <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="32"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>246</v>
-      </c>
-      <c r="C6" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B8" t="s">
-        <v>250</v>
-      </c>
-      <c r="C8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B9" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="C9" s="8">
-        <v>6.5883999999999998E-2</v>
-      </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="33"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>251</v>
-      </c>
-      <c r="D10" s="20"/>
-      <c r="E10" s="27"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B11" t="s">
-        <v>252</v>
-      </c>
-      <c r="C11" t="s">
-        <v>252</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8716025D-6040-4D17-B4EA-B59A0DAE7C7F}">
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="25" customWidth="1"/>
-    <col min="5" max="5" width="25" style="30" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="29"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="5">
-        <v>6.9999999999999999E-4</v>
-      </c>
-      <c r="C3" s="15">
-        <v>8.0000000000000004E-4</v>
-      </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="31"/>
-    </row>
-    <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>231</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="32"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>233</v>
-      </c>
-      <c r="C6" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" t="s">
-        <v>237</v>
-      </c>
-      <c r="C8" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B9" s="8">
-        <v>0.22220000000000001</v>
-      </c>
-      <c r="C9" s="8">
-        <v>0.695461</v>
-      </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="33"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="D10" s="20"/>
-      <c r="E10" s="27"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B11" t="s">
-        <v>240</v>
-      </c>
-      <c r="C11" t="s">
-        <v>240</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E46188D4-5281-4A43-BB5D-4640E9D5F481}">
-  <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="28.6640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="25" style="14" customWidth="1"/>
-    <col min="8" max="16384" width="9.109375" style="14"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
         <v>76</v>
       </c>
@@ -2956,7 +3308,7 @@
       <c r="F1" s="13"/>
       <c r="G1" s="13"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>7</v>
       </c>
@@ -2967,7 +3319,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>6</v>
       </c>
@@ -2982,7 +3334,7 @@
       <c r="F3" s="15"/>
       <c r="G3" s="15"/>
     </row>
-    <row r="4" spans="1:7" s="17" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>10</v>
       </c>
@@ -2993,7 +3345,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>11</v>
       </c>
@@ -3004,7 +3356,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>8</v>
       </c>
@@ -3015,7 +3367,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>60</v>
       </c>
@@ -3026,7 +3378,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>84</v>
       </c>
@@ -3037,7 +3389,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>87</v>
       </c>
@@ -3052,7 +3404,7 @@
       <c r="F9" s="18"/>
       <c r="G9" s="18"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>67</v>
       </c>
@@ -3067,7 +3419,7 @@
       <c r="F10" s="20"/>
       <c r="G10" s="20"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>90</v>
       </c>
@@ -3078,163 +3430,28 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="B12" s="15">
+        <v>0.1002</v>
+      </c>
+      <c r="C12" s="15">
+        <v>0.1002</v>
+      </c>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>256</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03540639-8045-412E-9AE6-2FBCCA2E681D}">
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="28.6640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="25" style="14" customWidth="1"/>
-    <col min="8" max="16384" width="9.109375" style="14"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B1" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="6">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="C3" s="6">
-        <v>2E-3</v>
-      </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-    </row>
-    <row r="4" spans="1:7" s="17" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" s="28">
-        <v>595749</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="B9" s="18">
-        <v>0.16361000000000001</v>
-      </c>
-      <c r="C9" s="18">
-        <v>0.21784200000000001</v>
-      </c>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -3243,37 +3460,28 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D8D8909-BC34-41A7-B910-1CE99C70A1C8}">
-  <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03540639-8045-412E-9AE6-2FBCCA2E681D}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="25" style="14" customWidth="1"/>
-    <col min="5" max="5" width="26.5546875" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" customWidth="1"/>
-    <col min="8" max="16384" width="9.109375" style="14"/>
+    <col min="1" max="1" width="28.7109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="25" style="14" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="F1" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="G1" s="14"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>7</v>
       </c>
@@ -3283,59 +3491,34 @@
       <c r="C2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="F2" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="14"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="15">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="C3" s="15">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="D3" s="15">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="F3" s="24">
-        <v>1.4E-3</v>
-      </c>
-      <c r="G3" s="14"/>
-    </row>
-    <row r="4" spans="1:7" s="17" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="C3" s="6">
+        <v>2E-3</v>
+      </c>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+    </row>
+    <row r="4" spans="1:7" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="F4" s="25" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>11</v>
       </c>
@@ -3345,60 +3528,30 @@
       <c r="C5" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="14"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="G6" s="14"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>60</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="G7" s="14"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+      <c r="C7" s="28">
+        <v>595749</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>84</v>
       </c>
@@ -3408,60 +3561,38 @@
       <c r="C8" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="D8" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="F8" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="G8" s="14"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>87</v>
       </c>
       <c r="B9" s="18">
-        <v>0.1225</v>
+        <v>0.16361000000000001</v>
       </c>
       <c r="C9" s="18">
-        <v>0.20618</v>
-      </c>
-      <c r="D9" s="18">
-        <v>0.3105</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="F9" s="26">
-        <v>0.43645800000000001</v>
-      </c>
-      <c r="G9" s="14"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.21784200000000001</v>
+      </c>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>67</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="F10" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="G10" s="14"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>90</v>
       </c>
@@ -3471,19 +3602,6 @@
       <c r="C11" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="D11" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="F11" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="G11" s="14"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G12" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3491,65 +3609,99 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94A797B-59DC-4A1F-AF3E-98233FCECA0A}">
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D8D8909-BC34-41A7-B910-1CE99C70A1C8}">
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="25" style="14" customWidth="1"/>
-    <col min="8" max="16384" width="9.109375" style="14"/>
+    <col min="1" max="1" width="28.7109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="25" style="14" customWidth="1"/>
+    <col min="5" max="5" width="26.5703125" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" style="23" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="G1" s="14"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D2" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="6">
-        <v>1.5E-3</v>
-      </c>
-      <c r="C3" s="6">
-        <v>3.8999999999999998E-3</v>
-      </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-    </row>
-    <row r="4" spans="1:7" s="17" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B3" s="15">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="C3" s="15">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="D3" s="15">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F3" s="24">
+        <v>1.4E-3</v>
+      </c>
+      <c r="G3" s="14"/>
+    </row>
+    <row r="4" spans="1:7" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>11</v>
       </c>
@@ -3559,30 +3711,60 @@
       <c r="C5" s="14" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D5" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="14"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>60</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="G7" s="14"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>84</v>
       </c>
@@ -3592,47 +3774,100 @@
       <c r="C8" s="14" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D8" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="G8" s="14"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>87</v>
       </c>
       <c r="B9" s="18">
-        <v>0.31519999999999998</v>
+        <v>0.1225</v>
       </c>
       <c r="C9" s="18">
-        <v>0.38289299999999998</v>
-      </c>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.20618</v>
+      </c>
+      <c r="D9" s="18">
+        <v>0.3105</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="F9" s="26">
+        <v>0.43645800000000001</v>
+      </c>
+      <c r="G9" s="14"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>67</v>
       </c>
       <c r="B10" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="D10" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="C10" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E10" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>90</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>73</v>
       </c>
+      <c r="D11" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="F11" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="G11" s="14"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="B12" s="15">
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="C12" s="15">
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="D12" s="15">
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="E12" s="15">
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="F12" s="15">
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="G12" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3640,65 +3875,65 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB20A0A9-7164-440A-BBB3-527A20A0F420}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94A797B-59DC-4A1F-AF3E-98233FCECA0A}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" style="12" bestFit="1" customWidth="1"/>
     <col min="2" max="7" width="25" style="14" customWidth="1"/>
-    <col min="8" max="16384" width="9.109375" style="14"/>
+    <col min="8" max="16384" width="9.140625" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="D1" s="13"/>
       <c r="E1" s="13"/>
       <c r="F1" s="13"/>
       <c r="G1" s="13"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="14" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="6">
-        <v>2.5000000000000001E-3</v>
+        <v>1.5E-3</v>
       </c>
       <c r="C3" s="6">
-        <v>2.5000000000000001E-3</v>
+        <v>3.8999999999999998E-3</v>
       </c>
       <c r="D3" s="15"/>
       <c r="E3" s="15"/>
       <c r="F3" s="15"/>
       <c r="G3" s="15"/>
     </row>
-    <row r="4" spans="1:7" s="17" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>11</v>
       </c>
@@ -3709,75 +3944,75 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>60</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>84</v>
       </c>
       <c r="B8" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="14" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>87</v>
       </c>
       <c r="B9" s="18">
-        <v>0.14660500000000001</v>
+        <v>0.31519999999999998</v>
       </c>
       <c r="C9" s="18">
-        <v>0.15989999999999999</v>
+        <v>0.38289299999999998</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="18"/>
       <c r="F9" s="18"/>
       <c r="G9" s="18"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>67</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="D10" s="20"/>
       <c r="E10" s="20"/>
       <c r="F10" s="20"/>
       <c r="G10" s="20"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>90</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>73</v>
@@ -3789,15 +4024,164 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB20A0A9-7164-440A-BBB3-527A20A0F420}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28.7109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="25" style="14" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B1" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="6">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="C3" s="6">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+    </row>
+    <row r="4" spans="1:7" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" s="18">
+        <v>0.14660500000000001</v>
+      </c>
+      <c r="C9" s="18">
+        <v>0.15989999999999999</v>
+      </c>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77E6AA59-FE92-44E5-B986-A9C890E75A2C}">
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="7" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
         <v>2</v>
       </c>
@@ -3817,7 +4201,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -3840,7 +4224,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -3863,7 +4247,7 @@
         <v>8.0000000000000004E-4</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>10</v>
       </c>
@@ -3886,7 +4270,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -3909,7 +4293,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -3932,7 +4316,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -3955,7 +4339,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>35</v>
       </c>
@@ -3978,7 +4362,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>36</v>
       </c>
@@ -4001,7 +4385,7 @@
         <v>0.21210300000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>40</v>
       </c>
@@ -4022,6 +4406,29 @@
       </c>
       <c r="G10" s="3" t="s">
         <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="B11" s="15">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="C11" s="15">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="D11" s="15">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="E11" s="15">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="F11" s="15">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="G11" s="15">
+        <v>0.27500000000000002</v>
       </c>
     </row>
   </sheetData>
@@ -4032,17 +4439,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BE1560A-CADF-4F3F-8D65-A406641ACDAB}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" style="12" bestFit="1" customWidth="1"/>
     <col min="2" max="7" width="25" style="14" customWidth="1"/>
-    <col min="8" max="16384" width="9.109375" style="14"/>
+    <col min="8" max="16384" width="9.140625" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
         <v>149</v>
       </c>
@@ -4054,7 +4461,7 @@
       <c r="F1" s="13"/>
       <c r="G1" s="13"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>7</v>
       </c>
@@ -4065,7 +4472,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>6</v>
       </c>
@@ -4080,7 +4487,7 @@
       <c r="F3" s="15"/>
       <c r="G3" s="15"/>
     </row>
-    <row r="4" spans="1:7" s="17" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>10</v>
       </c>
@@ -4091,7 +4498,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>11</v>
       </c>
@@ -4102,7 +4509,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>8</v>
       </c>
@@ -4113,7 +4520,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>60</v>
       </c>
@@ -4124,7 +4531,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>84</v>
       </c>
@@ -4135,7 +4542,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>87</v>
       </c>
@@ -4150,7 +4557,7 @@
       <c r="F9" s="18"/>
       <c r="G9" s="18"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>67</v>
       </c>
@@ -4165,161 +4572,12 @@
       <c r="F10" s="20"/>
       <c r="G10" s="20"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>90</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>75</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>73</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29CCCBDC-E4C7-4EFC-80EF-4EF2998B8A6B}">
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="28.6640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="25" style="14" customWidth="1"/>
-    <col min="8" max="16384" width="9.109375" style="14"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B1" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="6">
-        <v>3.5000000000000001E-3</v>
-      </c>
-      <c r="C3" s="6">
-        <v>3.5000000000000001E-3</v>
-      </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-    </row>
-    <row r="4" spans="1:7" s="17" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="B9" s="18">
-        <v>5.1310000000000001E-2</v>
-      </c>
-      <c r="C9" s="18">
-        <v>0.58701999999999999</v>
-      </c>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>74</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>73</v>
